--- a/data/processed/positivacao/2021-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2021-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24555,7 +24555,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B932" t="inlineStr"/>
@@ -36531,7 +36531,7 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr"/>
@@ -65241,7 +65241,7 @@
     <row r="2498">
       <c r="A2498" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2498" t="inlineStr"/>
@@ -66912,12 +66912,12 @@
       <c r="A2563" t="inlineStr"/>
       <c r="B2563" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 59 cliente(s), não positivou 775 cliente(s) - Total vendido: R$ 112.248,32
-Vendedor 3 - FERNANDA: positivou 97 cliente(s), não positivou 363 cliente(s) - Total vendido: R$ 89.527,90
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 651 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 97 cliente(s), não positivou 363 cliente(s) - Total vendido: R$ 89.527,90
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 651 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 452 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2563" t="inlineStr"/>
